--- a/backend/data/financials_by_company/0236.HK.xlsx
+++ b/backend/data/financials_by_company/0236.HK.xlsx
@@ -3642,187 +3642,187 @@
       </c>
       <c r="DB1" t="inlineStr">
         <is>
+          <t>hasPrePostMarketData</t>
+        </is>
+      </c>
+      <c r="DC1" t="inlineStr">
+        <is>
+          <t>firstTradeDateMilliseconds</t>
+        </is>
+      </c>
+      <c r="DD1" t="inlineStr">
+        <is>
+          <t>regularMarketChange</t>
+        </is>
+      </c>
+      <c r="DE1" t="inlineStr">
+        <is>
+          <t>regularMarketDayRange</t>
+        </is>
+      </c>
+      <c r="DF1" t="inlineStr">
+        <is>
+          <t>fullExchangeName</t>
+        </is>
+      </c>
+      <c r="DG1" t="inlineStr">
+        <is>
+          <t>averageDailyVolume3Month</t>
+        </is>
+      </c>
+      <c r="DH1" t="inlineStr">
+        <is>
+          <t>fiftyTwoWeekLowChange</t>
+        </is>
+      </c>
+      <c r="DI1" t="inlineStr">
+        <is>
+          <t>fiftyTwoWeekLowChangePercent</t>
+        </is>
+      </c>
+      <c r="DJ1" t="inlineStr">
+        <is>
+          <t>fiftyTwoWeekRange</t>
+        </is>
+      </c>
+      <c r="DK1" t="inlineStr">
+        <is>
+          <t>fiftyTwoWeekHighChange</t>
+        </is>
+      </c>
+      <c r="DL1" t="inlineStr">
+        <is>
+          <t>fiftyTwoWeekHighChangePercent</t>
+        </is>
+      </c>
+      <c r="DM1" t="inlineStr">
+        <is>
+          <t>fiftyTwoWeekChangePercent</t>
+        </is>
+      </c>
+      <c r="DN1" t="inlineStr">
+        <is>
+          <t>earningsTimestampStart</t>
+        </is>
+      </c>
+      <c r="DO1" t="inlineStr">
+        <is>
+          <t>earningsTimestampEnd</t>
+        </is>
+      </c>
+      <c r="DP1" t="inlineStr">
+        <is>
           <t>isEarningsDateEstimate</t>
         </is>
       </c>
-      <c r="DC1" t="inlineStr">
+      <c r="DQ1" t="inlineStr">
         <is>
           <t>epsTrailingTwelveMonths</t>
         </is>
       </c>
-      <c r="DD1" t="inlineStr">
+      <c r="DR1" t="inlineStr">
         <is>
           <t>fiftyDayAverageChange</t>
         </is>
       </c>
-      <c r="DE1" t="inlineStr">
+      <c r="DS1" t="inlineStr">
         <is>
           <t>fiftyDayAverageChangePercent</t>
         </is>
       </c>
-      <c r="DF1" t="inlineStr">
+      <c r="DT1" t="inlineStr">
         <is>
           <t>twoHundredDayAverageChange</t>
         </is>
       </c>
-      <c r="DG1" t="inlineStr">
+      <c r="DU1" t="inlineStr">
         <is>
           <t>twoHundredDayAverageChangePercent</t>
         </is>
       </c>
-      <c r="DH1" t="inlineStr">
+      <c r="DV1" t="inlineStr">
         <is>
           <t>sourceInterval</t>
         </is>
       </c>
-      <c r="DI1" t="inlineStr">
+      <c r="DW1" t="inlineStr">
         <is>
           <t>exchangeDataDelayedBy</t>
         </is>
       </c>
-      <c r="DJ1" t="inlineStr">
+      <c r="DX1" t="inlineStr">
         <is>
           <t>cryptoTradeable</t>
         </is>
       </c>
-      <c r="DK1" t="inlineStr">
+      <c r="DY1" t="inlineStr">
+        <is>
+          <t>marketState</t>
+        </is>
+      </c>
+      <c r="DZ1" t="inlineStr">
+        <is>
+          <t>regularMarketChangePercent</t>
+        </is>
+      </c>
+      <c r="EA1" t="inlineStr">
+        <is>
+          <t>regularMarketPrice</t>
+        </is>
+      </c>
+      <c r="EB1" t="inlineStr">
+        <is>
+          <t>longName</t>
+        </is>
+      </c>
+      <c r="EC1" t="inlineStr">
+        <is>
+          <t>corporateActions</t>
+        </is>
+      </c>
+      <c r="ED1" t="inlineStr">
+        <is>
+          <t>regularMarketTime</t>
+        </is>
+      </c>
+      <c r="EE1" t="inlineStr">
+        <is>
+          <t>exchange</t>
+        </is>
+      </c>
+      <c r="EF1" t="inlineStr">
+        <is>
+          <t>messageBoardId</t>
+        </is>
+      </c>
+      <c r="EG1" t="inlineStr">
+        <is>
+          <t>exchangeTimezoneName</t>
+        </is>
+      </c>
+      <c r="EH1" t="inlineStr">
+        <is>
+          <t>exchangeTimezoneShortName</t>
+        </is>
+      </c>
+      <c r="EI1" t="inlineStr">
+        <is>
+          <t>gmtOffSetMilliseconds</t>
+        </is>
+      </c>
+      <c r="EJ1" t="inlineStr">
+        <is>
+          <t>market</t>
+        </is>
+      </c>
+      <c r="EK1" t="inlineStr">
+        <is>
+          <t>esgPopulated</t>
+        </is>
+      </c>
+      <c r="EL1" t="inlineStr">
         <is>
           <t>shortName</t>
-        </is>
-      </c>
-      <c r="DL1" t="inlineStr">
-        <is>
-          <t>longName</t>
-        </is>
-      </c>
-      <c r="DM1" t="inlineStr">
-        <is>
-          <t>corporateActions</t>
-        </is>
-      </c>
-      <c r="DN1" t="inlineStr">
-        <is>
-          <t>regularMarketTime</t>
-        </is>
-      </c>
-      <c r="DO1" t="inlineStr">
-        <is>
-          <t>exchange</t>
-        </is>
-      </c>
-      <c r="DP1" t="inlineStr">
-        <is>
-          <t>messageBoardId</t>
-        </is>
-      </c>
-      <c r="DQ1" t="inlineStr">
-        <is>
-          <t>exchangeTimezoneName</t>
-        </is>
-      </c>
-      <c r="DR1" t="inlineStr">
-        <is>
-          <t>exchangeTimezoneShortName</t>
-        </is>
-      </c>
-      <c r="DS1" t="inlineStr">
-        <is>
-          <t>gmtOffSetMilliseconds</t>
-        </is>
-      </c>
-      <c r="DT1" t="inlineStr">
-        <is>
-          <t>market</t>
-        </is>
-      </c>
-      <c r="DU1" t="inlineStr">
-        <is>
-          <t>esgPopulated</t>
-        </is>
-      </c>
-      <c r="DV1" t="inlineStr">
-        <is>
-          <t>hasPrePostMarketData</t>
-        </is>
-      </c>
-      <c r="DW1" t="inlineStr">
-        <is>
-          <t>firstTradeDateMilliseconds</t>
-        </is>
-      </c>
-      <c r="DX1" t="inlineStr">
-        <is>
-          <t>regularMarketChange</t>
-        </is>
-      </c>
-      <c r="DY1" t="inlineStr">
-        <is>
-          <t>regularMarketDayRange</t>
-        </is>
-      </c>
-      <c r="DZ1" t="inlineStr">
-        <is>
-          <t>fullExchangeName</t>
-        </is>
-      </c>
-      <c r="EA1" t="inlineStr">
-        <is>
-          <t>averageDailyVolume3Month</t>
-        </is>
-      </c>
-      <c r="EB1" t="inlineStr">
-        <is>
-          <t>fiftyTwoWeekLowChange</t>
-        </is>
-      </c>
-      <c r="EC1" t="inlineStr">
-        <is>
-          <t>fiftyTwoWeekLowChangePercent</t>
-        </is>
-      </c>
-      <c r="ED1" t="inlineStr">
-        <is>
-          <t>fiftyTwoWeekRange</t>
-        </is>
-      </c>
-      <c r="EE1" t="inlineStr">
-        <is>
-          <t>fiftyTwoWeekHighChange</t>
-        </is>
-      </c>
-      <c r="EF1" t="inlineStr">
-        <is>
-          <t>fiftyTwoWeekHighChangePercent</t>
-        </is>
-      </c>
-      <c r="EG1" t="inlineStr">
-        <is>
-          <t>fiftyTwoWeekChangePercent</t>
-        </is>
-      </c>
-      <c r="EH1" t="inlineStr">
-        <is>
-          <t>earningsTimestampStart</t>
-        </is>
-      </c>
-      <c r="EI1" t="inlineStr">
-        <is>
-          <t>earningsTimestampEnd</t>
-        </is>
-      </c>
-      <c r="EJ1" t="inlineStr">
-        <is>
-          <t>regularMarketChangePercent</t>
-        </is>
-      </c>
-      <c r="EK1" t="inlineStr">
-        <is>
-          <t>regularMarketPrice</t>
-        </is>
-      </c>
-      <c r="EL1" t="inlineStr">
-        <is>
-          <t>marketState</t>
         </is>
       </c>
       <c r="EM1" t="inlineStr">
@@ -3925,10 +3925,10 @@
         <v>3</v>
       </c>
       <c r="U2" t="n">
-        <v>1.19</v>
+        <v>1.21</v>
       </c>
       <c r="V2" t="n">
-        <v>1.19</v>
+        <v>1.2</v>
       </c>
       <c r="W2" t="n">
         <v>1.19</v>
@@ -3937,10 +3937,10 @@
         <v>1.2</v>
       </c>
       <c r="Y2" t="n">
-        <v>1.19</v>
+        <v>1.21</v>
       </c>
       <c r="Z2" t="n">
-        <v>1.19</v>
+        <v>1.2</v>
       </c>
       <c r="AA2" t="n">
         <v>1.19</v>
@@ -3952,7 +3952,7 @@
         <v>0.06</v>
       </c>
       <c r="AD2" t="n">
-        <v>5</v>
+        <v>4.96</v>
       </c>
       <c r="AE2" t="n">
         <v>1776988800</v>
@@ -3961,31 +3961,31 @@
         <v>0.25</v>
       </c>
       <c r="AG2" t="n">
-        <v>0.217</v>
+        <v>0.2</v>
       </c>
       <c r="AH2" t="n">
-        <v>6</v>
+        <v>5.9500003</v>
       </c>
       <c r="AI2" t="n">
-        <v>36150</v>
+        <v>8000</v>
       </c>
       <c r="AJ2" t="n">
-        <v>36150</v>
+        <v>8000</v>
       </c>
       <c r="AK2" t="n">
-        <v>27097</v>
+        <v>26397</v>
       </c>
       <c r="AL2" t="n">
-        <v>16437</v>
+        <v>15237</v>
       </c>
       <c r="AM2" t="n">
-        <v>16437</v>
+        <v>15237</v>
       </c>
       <c r="AN2" t="n">
         <v>1.12</v>
       </c>
       <c r="AO2" t="n">
-        <v>1.26</v>
+        <v>1.19</v>
       </c>
       <c r="AP2" t="n">
         <v>0</v>
@@ -3994,10 +3994,10 @@
         <v>0</v>
       </c>
       <c r="AR2" t="n">
-        <v>448284704</v>
+        <v>444548992</v>
       </c>
       <c r="AS2" t="n">
-        <v>448284672</v>
+        <v>455756083</v>
       </c>
       <c r="AT2" t="n">
         <v>0.85</v>
@@ -4012,10 +4012,10 @@
         <v>0.6</v>
       </c>
       <c r="AX2" t="n">
-        <v>0.6079912</v>
+        <v>0.6029246</v>
       </c>
       <c r="AY2" t="n">
-        <v>1.2292</v>
+        <v>1.226</v>
       </c>
       <c r="AZ2" t="n">
         <v>1.2297</v>
@@ -4024,7 +4024,7 @@
         <v>0.06</v>
       </c>
       <c r="BB2" t="n">
-        <v>0.050420165</v>
+        <v>0.049586773</v>
       </c>
       <c r="BC2" t="inlineStr">
         <is>
@@ -4035,7 +4035,7 @@
         <v>0</v>
       </c>
       <c r="BE2" t="n">
-        <v>148787680</v>
+        <v>145051968</v>
       </c>
       <c r="BF2" t="n">
         <v>0.103240006</v>
@@ -4059,7 +4059,7 @@
         <v>1.92</v>
       </c>
       <c r="BM2" t="n">
-        <v>0.62500006</v>
+        <v>0.6197916999999999</v>
       </c>
       <c r="BN2" t="n">
         <v>1767139200</v>
@@ -4077,16 +4077,16 @@
         <v>0.2</v>
       </c>
       <c r="BS2" t="n">
-        <v>0.202</v>
+        <v>0.197</v>
       </c>
       <c r="BT2" t="n">
-        <v>1.523</v>
+        <v>1.485</v>
       </c>
       <c r="BU2" t="n">
-        <v>0.36363637</v>
+        <v>0.3444444</v>
       </c>
       <c r="BV2" t="n">
-        <v>0.27294624</v>
+        <v>0.22635591</v>
       </c>
       <c r="BW2" t="n">
         <v>0.06</v>
@@ -4100,7 +4100,7 @@
         </is>
       </c>
       <c r="BZ2" t="n">
-        <v>1.2</v>
+        <v>1.19</v>
       </c>
       <c r="CA2" t="inlineStr">
         <is>
@@ -4203,135 +4203,135 @@
         <v>0</v>
       </c>
       <c r="DC2" t="n">
+        <v>946949400000</v>
+      </c>
+      <c r="DD2" t="n">
+        <v>-0.01999998</v>
+      </c>
+      <c r="DE2" t="inlineStr">
+        <is>
+          <t>1.19 - 1.2</t>
+        </is>
+      </c>
+      <c r="DF2" t="inlineStr">
+        <is>
+          <t>HKSE</t>
+        </is>
+      </c>
+      <c r="DG2" t="n">
+        <v>26397</v>
+      </c>
+      <c r="DH2" t="n">
+        <v>0.34000003</v>
+      </c>
+      <c r="DI2" t="n">
+        <v>0.40000004</v>
+      </c>
+      <c r="DJ2" t="inlineStr">
+        <is>
+          <t>0.85 - 1.4</t>
+        </is>
+      </c>
+      <c r="DK2" t="n">
+        <v>-0.20999992</v>
+      </c>
+      <c r="DL2" t="n">
+        <v>-0.14999995</v>
+      </c>
+      <c r="DM2" t="n">
+        <v>34.44444</v>
+      </c>
+      <c r="DN2" t="n">
+        <v>1740407385</v>
+      </c>
+      <c r="DO2" t="n">
+        <v>1740407385</v>
+      </c>
+      <c r="DP2" t="b">
+        <v>0</v>
+      </c>
+      <c r="DQ2" t="n">
         <v>0.2</v>
       </c>
-      <c r="DD2" t="n">
-        <v>-0.029199958</v>
-      </c>
-      <c r="DE2" t="n">
-        <v>-0.023755254</v>
-      </c>
-      <c r="DF2" t="n">
-        <v>-0.029699922</v>
-      </c>
-      <c r="DG2" t="n">
-        <v>-0.024152169</v>
-      </c>
-      <c r="DH2" t="n">
+      <c r="DR2" t="n">
+        <v>-0.035999894</v>
+      </c>
+      <c r="DS2" t="n">
+        <v>-0.0293637</v>
+      </c>
+      <c r="DT2" t="n">
+        <v>-0.039699912</v>
+      </c>
+      <c r="DU2" t="n">
+        <v>-0.032284226</v>
+      </c>
+      <c r="DV2" t="n">
         <v>15</v>
       </c>
-      <c r="DI2" t="n">
+      <c r="DW2" t="n">
         <v>15</v>
       </c>
-      <c r="DJ2" t="b">
+      <c r="DX2" t="b">
         <v>0</v>
       </c>
-      <c r="DK2" t="inlineStr">
+      <c r="DY2" t="inlineStr">
+        <is>
+          <t>PREPRE</t>
+        </is>
+      </c>
+      <c r="DZ2" t="n">
+        <v>-1.652891</v>
+      </c>
+      <c r="EA2" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="EB2" t="inlineStr">
+        <is>
+          <t>San Miguel Brewery Hong Kong Limited</t>
+        </is>
+      </c>
+      <c r="EC2" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="ED2" t="n">
+        <v>1780991397</v>
+      </c>
+      <c r="EE2" t="inlineStr">
+        <is>
+          <t>HKG</t>
+        </is>
+      </c>
+      <c r="EF2" t="inlineStr">
+        <is>
+          <t>finmb_874762</t>
+        </is>
+      </c>
+      <c r="EG2" t="inlineStr">
+        <is>
+          <t>Asia/Hong_Kong</t>
+        </is>
+      </c>
+      <c r="EH2" t="inlineStr">
+        <is>
+          <t>HKT</t>
+        </is>
+      </c>
+      <c r="EI2" t="n">
+        <v>28800000</v>
+      </c>
+      <c r="EJ2" t="inlineStr">
+        <is>
+          <t>hk_market</t>
+        </is>
+      </c>
+      <c r="EK2" t="b">
+        <v>0</v>
+      </c>
+      <c r="EL2" t="inlineStr">
         <is>
           <t>SAN MIGUEL HK</t>
-        </is>
-      </c>
-      <c r="DL2" t="inlineStr">
-        <is>
-          <t>San Miguel Brewery Hong Kong Limited</t>
-        </is>
-      </c>
-      <c r="DM2" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="DN2" t="n">
-        <v>1780293153</v>
-      </c>
-      <c r="DO2" t="inlineStr">
-        <is>
-          <t>HKG</t>
-        </is>
-      </c>
-      <c r="DP2" t="inlineStr">
-        <is>
-          <t>finmb_874762</t>
-        </is>
-      </c>
-      <c r="DQ2" t="inlineStr">
-        <is>
-          <t>Asia/Hong_Kong</t>
-        </is>
-      </c>
-      <c r="DR2" t="inlineStr">
-        <is>
-          <t>HKT</t>
-        </is>
-      </c>
-      <c r="DS2" t="n">
-        <v>28800000</v>
-      </c>
-      <c r="DT2" t="inlineStr">
-        <is>
-          <t>hk_market</t>
-        </is>
-      </c>
-      <c r="DU2" t="b">
-        <v>0</v>
-      </c>
-      <c r="DV2" t="b">
-        <v>0</v>
-      </c>
-      <c r="DW2" t="n">
-        <v>946949400000</v>
-      </c>
-      <c r="DX2" t="n">
-        <v>0.00999999</v>
-      </c>
-      <c r="DY2" t="inlineStr">
-        <is>
-          <t>1.19 - 1.2</t>
-        </is>
-      </c>
-      <c r="DZ2" t="inlineStr">
-        <is>
-          <t>HKSE</t>
-        </is>
-      </c>
-      <c r="EA2" t="n">
-        <v>27097</v>
-      </c>
-      <c r="EB2" t="n">
-        <v>0.35000002</v>
-      </c>
-      <c r="EC2" t="n">
-        <v>0.4117647</v>
-      </c>
-      <c r="ED2" t="inlineStr">
-        <is>
-          <t>0.85 - 1.4</t>
-        </is>
-      </c>
-      <c r="EE2" t="n">
-        <v>-0.19999993</v>
-      </c>
-      <c r="EF2" t="n">
-        <v>-0.14285709</v>
-      </c>
-      <c r="EG2" t="n">
-        <v>36.363636</v>
-      </c>
-      <c r="EH2" t="n">
-        <v>1740407385</v>
-      </c>
-      <c r="EI2" t="n">
-        <v>1740407385</v>
-      </c>
-      <c r="EJ2" t="n">
-        <v>0.84033525</v>
-      </c>
-      <c r="EK2" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="EL2" t="inlineStr">
-        <is>
-          <t>PREPRE</t>
         </is>
       </c>
       <c r="EM2" t="inlineStr"/>
